--- a/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
+++ b/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
+    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
+++ b/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
@@ -12,6 +12,7 @@
     <sheet name="_meta" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="false" name="Interest_Total" vbProcedure="false">Schedule!$D$30</definedName>
     <definedName function="false" hidden="false" name="Ledger_DemoToday" vbProcedure="false">_meta!$B$4</definedName>
     <definedName function="false" hidden="false" name="Schedule_LastRow" vbProcedure="false">Schedule!$A$28</definedName>
     <definedName function="false" hidden="false" name="Snapshot_Date" vbProcedure="false">Schedule!$B$2</definedName>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
   <si>
     <t xml:space="preserve">Ödeme Planı — Yeşilova RES</t>
   </si>
@@ -43,6 +44,9 @@
     <t xml:space="preserve">Anapara (USD)</t>
   </si>
   <si>
+    <t xml:space="preserve">Faiz (USD)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Durum (bu anlık görüntüye göre)</t>
   </si>
   <si>
@@ -52,13 +56,22 @@
     <t xml:space="preserve">Bekliyor</t>
   </si>
   <si>
+    <t xml:space="preserve">Faiz toplamı (yalnız ledger'da verilen satırlar):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ledger'da bağımsız bir 'toplam faiz' alanı yok (karşılaştırılacak bir referans değer yok) — yalnız taksit #11 için tek bir faiz değeri verilmiş; diğer taksitler boş, türetilmedi.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DEMO — synthetic demo workbook (Company AI V0); figures are fictional</t>
   </si>
   <si>
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
+    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -151,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -162,6 +175,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -181,10 +198,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -213,6 +232,9 @@
       <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
@@ -224,8 +246,8 @@
       <c r="C5" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>6</v>
+      <c r="E5" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -238,8 +260,8 @@
       <c r="C6" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>6</v>
+      <c r="E6" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -252,8 +274,8 @@
       <c r="C7" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>6</v>
+      <c r="E7" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -266,8 +288,8 @@
       <c r="C8" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>6</v>
+      <c r="E8" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -280,8 +302,8 @@
       <c r="C9" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>6</v>
+      <c r="E9" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -294,8 +316,8 @@
       <c r="C10" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>6</v>
+      <c r="E10" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -308,8 +330,8 @@
       <c r="C11" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>6</v>
+      <c r="E11" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -322,8 +344,8 @@
       <c r="C12" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>6</v>
+      <c r="E12" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -336,8 +358,8 @@
       <c r="C13" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>6</v>
+      <c r="E13" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -350,8 +372,8 @@
       <c r="C14" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>6</v>
+      <c r="E14" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -364,8 +386,11 @@
       <c r="C15" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>7</v>
+      <c r="D15" s="0" t="n">
+        <v>18240</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -378,8 +403,8 @@
       <c r="C16" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>7</v>
+      <c r="E16" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -392,8 +417,8 @@
       <c r="C17" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>7</v>
+      <c r="E17" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -406,8 +431,8 @@
       <c r="C18" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>7</v>
+      <c r="E18" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -420,8 +445,8 @@
       <c r="C19" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>7</v>
+      <c r="E19" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -434,8 +459,8 @@
       <c r="C20" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>7</v>
+      <c r="E20" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -448,8 +473,8 @@
       <c r="C21" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>7</v>
+      <c r="E21" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -462,8 +487,8 @@
       <c r="C22" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>7</v>
+      <c r="E22" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -476,8 +501,8 @@
       <c r="C23" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>7</v>
+      <c r="E23" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -490,8 +515,8 @@
       <c r="C24" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>7</v>
+      <c r="E24" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -504,8 +529,8 @@
       <c r="C25" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>7</v>
+      <c r="E25" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -518,8 +543,8 @@
       <c r="C26" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>7</v>
+      <c r="E26" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -532,8 +557,8 @@
       <c r="C27" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>7</v>
+      <c r="E27" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -546,8 +571,25 @@
       <c r="C28" s="0" t="n">
         <v>98000</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>7</v>
+      <c r="E28" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <f aca="false">SUM(D15)</f>
+        <v>18240</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -571,20 +613,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
@@ -592,10 +634,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
+++ b/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
@@ -12,7 +12,6 @@
     <sheet name="_meta" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="Interest_Total" vbProcedure="false">Schedule!$D$30</definedName>
     <definedName function="false" hidden="false" name="Ledger_DemoToday" vbProcedure="false">_meta!$B$4</definedName>
     <definedName function="false" hidden="false" name="Schedule_LastRow" vbProcedure="false">Schedule!$A$28</definedName>
     <definedName function="false" hidden="false" name="Snapshot_Date" vbProcedure="false">Schedule!$B$2</definedName>
@@ -71,7 +70,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
+    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -579,10 +578,6 @@
       <c r="C30" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="0" t="n">
-        <f aca="false">SUM(D15)</f>
-        <v>18240</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="0" t="s">

--- a/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
+++ b/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
+    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
+++ b/seed_data/excel/Yesilova_Repayment_Schedule_2026-09.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
+    <t xml:space="preserve">2026-10-12T13:12:20+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
